--- a/public/result_files/results_CircuitBreakerCalculateSample.xlsx
+++ b/public/result_files/results_CircuitBreakerCalculateSample.xlsx
@@ -398,26 +398,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>MachineNum</v>
+        <v>Machines number</v>
       </c>
       <c r="B1" t="str">
-        <v>watt</v>
+        <v>Power</v>
       </c>
       <c r="C1" t="str">
-        <v>WattUnit</v>
+        <v>Power unit</v>
       </c>
       <c r="D1" t="str">
         <v>Voltage</v>
       </c>
       <c r="E1" t="str">
-        <v>powerFactor</v>
+        <v>Power factor</v>
       </c>
       <c r="F1" t="str">
-        <v>phases</v>
+        <v>Phases</v>
       </c>
       <c r="G1" t="str">
         <v>Current Intensity</v>
@@ -434,33 +434,62 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C2" t="str">
-        <v xml:space="preserve">HP </v>
+        <v xml:space="preserve">KW </v>
       </c>
       <c r="D2">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E2">
         <v>0.9</v>
       </c>
       <c r="F2" t="str">
+        <v>three phases</v>
+      </c>
+      <c r="G2">
+        <v>200.70648683365445</v>
+      </c>
+      <c r="H2" t="str">
+        <v>400A</v>
+      </c>
+      <c r="I2" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3" t="str">
+        <v xml:space="preserve">W </v>
+      </c>
+      <c r="D3">
+        <v>220</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
         <v xml:space="preserve">one phase </v>
       </c>
-      <c r="G2">
-        <v>33.90909090909091</v>
-      </c>
-      <c r="H2" t="str">
-        <v>50A</v>
-      </c>
-      <c r="I2">
-        <v>16</v>
+      <c r="G3">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="H3" t="str">
+        <v>6A</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/result_files/results_CircuitBreakerCalculateSample.xlsx
+++ b/public/result_files/results_CircuitBreakerCalculateSample.xlsx
@@ -448,14 +448,14 @@
       <c r="F2" t="str">
         <v>three phases</v>
       </c>
-      <c r="G2">
-        <v>200.70648683365445</v>
+      <c r="G2" t="str">
+        <v>200.71</v>
       </c>
       <c r="H2" t="str">
-        <v>400A</v>
-      </c>
-      <c r="I2" t="str">
-        <v>unknown</v>
+        <v>250A</v>
+      </c>
+      <c r="I2">
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -477,8 +477,8 @@
       <c r="F3" t="str">
         <v xml:space="preserve">one phase </v>
       </c>
-      <c r="G3">
-        <v>0.36363636363636365</v>
+      <c r="G3" t="str">
+        <v>0.36</v>
       </c>
       <c r="H3" t="str">
         <v>6A</v>
